--- a/myG All Store.xlsx
+++ b/myG All Store.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>Store</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>ATTINGAL FUTURE</t>
+  </si>
+  <si>
+    <t>CHEMMAD FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1667,7 +1670,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A141"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6666666666667" customWidth="1"/>
@@ -2369,13 +2372,18 @@
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="8" t="s">
+      <c r="A140" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="5" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/myG All Store.xlsx
+++ b/myG All Store.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Store</t>
   </si>
@@ -459,6 +459,9 @@
   </si>
   <si>
     <t>FALNIR FUTURE</t>
+  </si>
+  <si>
+    <t>THRIPUNITHURA FUTURE</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1142,9 +1145,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1159,7 +1159,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1679,7 +1679,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A144"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6666666666667" customWidth="1"/>
@@ -2396,13 +2396,18 @@
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="9" t="s">
+      <c r="A144" s="7" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="8" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
